--- a/光伏配储项目/电价数据/2026/尖峰站.xlsx
+++ b/光伏配储项目/电价数据/2026/尖峰站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5541900000000001</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38009</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.6326</v>
+      </c>
+      <c r="D117" t="n">
+        <v>1.01388</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1.17143</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.12915</v>
+      </c>
+      <c r="G117" t="n">
+        <v>1.08091</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.93555</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.9406100000000001</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44043</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.6295299999999999</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.68245</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.61512</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.92038</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.9153300000000001</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.60841</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.9298500000000001</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.9246799999999999</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.90504</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.91859</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.6395299999999999</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.9261699999999999</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39494</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.63735</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.92515</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.9311699999999999</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.6607799999999999</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.9559299999999999</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>1.04249</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.4046</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.88562</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.6942699999999999</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.6887000000000001</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.31644</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.4694700000000001</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.75625</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.7794099999999999</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.4038</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.39239</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>1.04702</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>1.03587</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>1.12748</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.7597</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.32536</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.72123</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.50813</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.4104</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.40677</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.41109</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.79235</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.98372</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.34623</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.53061</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.7833600000000001</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.42982</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.79159</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.76515</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.95958</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.92367</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>1.07521</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>1.35094</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.2023</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.23778</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.74788</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.25183</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>1.19496</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>1.1056</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>1.2543</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.54923</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>1.19789</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.28132</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.49864</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.33833</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.25819</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.43811</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.37884</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.31093</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.81697</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47924</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.41064</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.4127</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.4219</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.19073</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1.04552</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.18241</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53623</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5226499999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50627</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5159900000000001</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.7050700000000001</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.6071299999999999</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.6793899999999999</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.5857599999999999</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.34292</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.57745</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.65418</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.61779</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.6233300000000001</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.62329</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.61788</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.61239</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.66771</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.92315</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.2554</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.9308099999999999</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.6832999999999999</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.57692</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.63681</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.5472400000000001</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.57512</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.96014</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>1.17329</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.79857</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>1.13061</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>1.05883</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>1.02021</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.7259500000000001</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.5552</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.57773</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.6974900000000001</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.35202</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>1.19696</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>1.2634</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.5129</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>1.19319</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.66692</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>1.09165</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.8438600000000001</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.27707</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.16744</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.2961</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.31658</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.62586</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.6517200000000001</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.5756599999999999</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.62695</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1.20733</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>1.20057</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.20827</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>1.20153</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.99946</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.18396</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.19904</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.19527</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.67542</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.19564</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.20776</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.26063</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.5585</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.47369</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.20091</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.50667</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.26622</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.7553799999999999</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.7639199999999999</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44059</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43462</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41377</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35425</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33341</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.6722400000000001</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.8083400000000001</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.79061</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.58902</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.65854</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.5741499999999999</v>
+      </c>
+      <c r="I119" t="n">
+        <v>1.18818</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.76061</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.75218</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.7121499999999999</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.65567</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.78107</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.6075199999999999</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.75402</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.56329</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37974</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.6565</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.58245</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.64666</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.6133</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.6035199999999999</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.6144299999999999</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.61952</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.55328</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.70682</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.83912</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.11934</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.88128</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.7656900000000001</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.71349</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.60915</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.3078</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.30097</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.6415599999999999</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.42636</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.7446</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>1.18313</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.55863</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.6955399999999999</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>1.19141</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.66831</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.19527</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>1.19711</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.80799</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.97222</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.19874</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>1.19891</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.90725</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.56304</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.41461</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.47699</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.67949</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>1.18724</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>1.05175</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>1.19739</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.43736</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.27967</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>1.19658</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.22292</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>1.21411</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.44525</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.29132</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.30647</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.66856</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.21336</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>1.21165</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>1.06868</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>1.10168</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.12254</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1.10861</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>1.23708</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>1.19351</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.28042</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>1.02204</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.7263099999999999</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.5380900000000001</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.41301</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34314</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1.16312</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.82587</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.8100599999999999</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.76153</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.78128</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.951</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.6333799999999999</v>
+      </c>
+      <c r="J120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.73627</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.63847</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.80375</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.75515</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.69286</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.6253200000000001</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.62181</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.4654700000000001</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.54575</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.47506</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32518</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.4846</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34348</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.63001</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.62774</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.72712</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.6130599999999999</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.5866699999999999</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.5481900000000001</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.51998</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.6865599999999999</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.7240599999999999</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.94153</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>1.19427</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.33747</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.8613099999999999</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.57981</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.67199</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.9124800000000001</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.8925599999999999</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.18812</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.44686</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.77876</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.98537</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>1.24527</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.70821</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.1185</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.52998</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.49219</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.66899</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>1.02387</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>1.12572</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>1.26486</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>1.19731</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>1.09769</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>1.01334</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>1.03454</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.99849</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>1.29328</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>1.47489</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.8129299999999999</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.38043</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>1.23119</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.86476</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>1.10446</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>1.18493</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>1.1334</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>1.187</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>1.28395</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.34457</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>1.18685</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.29788</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>1.20292</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>1.19146</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>1.18609</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>1.21459</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>1.22573</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>1.21141</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>1.1885</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>1.18891</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.74161</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.53104</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.7456</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.33247</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.33201</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.33736</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32196</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.74959</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.49926</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.4062</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36483</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34515</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.34199</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.34064</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.33611</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.33735</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.33485</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.33527</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.33373</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.33404</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.33321</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.33257</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.33191</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.33276</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.33298</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33742</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.33527</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.48418</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.51073</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.52999</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.4054700000000001</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.46409</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.43282</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.4621499999999999</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.72763</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.86087</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.62449</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.7126</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.34549</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.7380099999999999</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.33784</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.85842</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.71617</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.55947</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.55851</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.54711</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.60172</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.47823</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.10085</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.33174</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.30943</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.29231</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.28487</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.31407</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.33577</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.55574</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.49125</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.5226499999999999</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.46889</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.64871</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.5116499999999999</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.49131</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.40291</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.49173</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.49505</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.60758</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.40612</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.51285</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.51191</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.4094</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.49108</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.35519</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.41077</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39844</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40988</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.38185</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.40541</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34427</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.2171</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.99458</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1.00974</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.5987100000000001</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.72009</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.66477</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.62298</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.66395</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.3643</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.64801</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.6468400000000001</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.91959</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.65485</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.65513</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.64601</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.64654</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.64683</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.27765</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.07482</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.31088</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04281</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04375</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04318</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04177</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.04654</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.27493</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.08395999999999999</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.29634</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.13101</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04294</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04456</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04663</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04652000000000001</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>0.00354</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04631</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04513</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04233</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.30756</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04552</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.30543</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.30893</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.26763</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.28482</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.3420899999999999</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.29618</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.39219</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.42973</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.36508</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.36574</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.35873</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.35845</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.44843</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.69264</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.66272</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.36335</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.39394</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.39021</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.36437</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.39411</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.67486</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.6636299999999999</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.66322</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.34118</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.36773</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.39756</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33455</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.65673</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.57243</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.4055299999999999</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34484</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31714</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.32097</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.27808</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.30823</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.30659</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.30565</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.30435</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.30833</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.29081</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.28701</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17179</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16014</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15938</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23743</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21479</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.29353</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27446</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.30817</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.31126</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.31205</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.31554</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.31539</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.30427</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.32916</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.33656</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.38867</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.76306</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.8997000000000001</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.69256</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.66662</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.68431</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.76688</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.96477</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.41093</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.36411</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.48386</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.74533</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.74817</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.91149</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.67045</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.54714</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.48497</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.45628</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.09354000000000001</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.2967</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.30306</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.3813</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.74425</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.7489</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.65365</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.61349</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.48067</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.73919</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7908500000000001</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.7904800000000001</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.6100599999999999</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.7534999999999999</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>1.02996</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.42964</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.85995</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.45911</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.34422</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.8106</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.40465</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>1.06376</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.42499</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.78649</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.46392</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.78631</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.80099</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5303600000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78769</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78551</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87858</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87912</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50254</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41209</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41209</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.46074</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.2192</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6393799999999999</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5414</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.70788</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.6837000000000001</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.67352</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.6778500000000001</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.68152</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.59927</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.68237</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.67183</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.56067</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.5655800000000001</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.57197</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38635</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.66226</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.64824</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.64811</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.64618</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.6470499999999999</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.6659700000000001</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.64762</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.6575800000000001</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.56264</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.72638</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.5656</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.60019</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.4374</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59623</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.5647300000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6669400000000001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>1.07812</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.6468700000000001</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.50863</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.57641</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.59693</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>1.00898</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.34224</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.31076</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.27319</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.5610299999999999</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.80035</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.57628</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.65607</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.55789</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.98712</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.7866299999999999</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.7353500000000001</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.6507200000000001</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.58299</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>1.01951</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>1.04941</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.5681799999999999</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.71809</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.6658500000000001</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.7360800000000001</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.6651900000000001</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.7111499999999999</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.80536</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.6978</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.7101000000000001</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.6081599999999999</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.5910599999999999</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.70982</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.7400599999999999</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.70933</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.73661</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.74563</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.7830900000000001</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.74083</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.78883</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.74566</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.74742</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.74651</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.7358899999999999</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.7301</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.71209</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.7300399999999999</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.69792</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.66439</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.70329</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.66932</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.68211</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.67008</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.66252</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.6572</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.56001</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.95612</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.6567000000000001</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.76861</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.75215</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.80791</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.6505599999999999</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.65863</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.59405</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.63027</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.37514</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.36408</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.5655800000000001</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.6627799999999999</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.41103</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.53171</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.62919</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.74887</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.89843</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>1.15056</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.5595800000000001</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.12496</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.8664700000000001</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.9747100000000001</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.88378</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.6532100000000001</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.83373</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>1.09532</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.34445</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.66051</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.5333300000000001</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.4377200000000001</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.38152</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.37776</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.90218</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>1.11038</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.77161</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>1.23318</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.80621</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.83728</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.84437</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.75922</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.40809</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.39291</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.37635</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.47785</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.39548</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.38112</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.36516</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.44476</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.38322</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.34444</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.37109</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.39764</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.50052</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.42038</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.41585</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.34461</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59675</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.20026</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.51762</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70359</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79534</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64979</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5836399999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5005500000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.8028</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.43894</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.76879</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.18911</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.93399</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.65699</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.78016</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.7143699999999999</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.57687</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.1766</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.63385</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.92183</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.5982799999999999</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.6881</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.43965</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.36314</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>1.33113</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>1.62068</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>1.11231</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.5405</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.34407</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.61549</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.8716</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1.52742</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.76322</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>1.09531</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>1.09405</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.9392200000000001</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.99538</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.94924</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.186</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>1.18302</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.88703</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>1.18314</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.62956</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.99573</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>1.03975</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>1.18311</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.97612</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>1.01699</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.60657</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.94868</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>1.00561</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>1.11286</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.91007</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.8977000000000001</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>1.12251</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.60908</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.98449</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>1.02144</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.75748</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38618</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36887</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.3405899999999999</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.33721</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.74334</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.61084</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.61261</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.34239</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.33728</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.33689</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.33851</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.33723</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.33528</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.33406</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.33701</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.33122</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.33505</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.59819</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.51706</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.63297</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33721</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.39399</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.3425</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.76144</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.6198400000000001</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.58602</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.61515</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.58861</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.63475</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.83565</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.7212799999999999</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.7143699999999999</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.66364</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.9873099999999999</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>1.19773</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.66573</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.66808</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.66983</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.60563</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.60702</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.66115</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.75467</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.72727</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.66569</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.5475800000000001</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.54137</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.55116</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.5534600000000001</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.37218</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.37944</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.40319</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36158</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.40541</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.61533</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.59838</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40188</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45672</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43992</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4392799999999999</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.4442</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.5992799999999999</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.59722</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.59763</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34934</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.58853</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.49548</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46869</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42386</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41593</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37014</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.5300900000000001</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.7241299999999999</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.65471</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.65825</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.65138</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.6743899999999999</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.5886699999999999</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.62187</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.51467</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.4461</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.51397</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.44611</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.6269400000000001</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.65634</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.6548200000000001</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.6382899999999999</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.5850700000000001</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.57828</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.54692</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34414</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34866</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.3755</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29474</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31695</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31689</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29398</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.55838</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.29404</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.35736</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.28215</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26677</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30023</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30816</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.3066</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31891</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.47315</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30696</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.33134</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31455</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.36542</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.31411</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.38382</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.48701</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.7052</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.6056699999999999</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.6266499999999999</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.8471799999999999</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>1.26815</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>1.16346</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.8503999999999999</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.45043</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.39629</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.42855</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.70025</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.93821</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.16517</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.1191</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.01583</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.5412400000000001</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.4386</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.42937</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.39697</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.37969</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41952</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.49694</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.44716</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.41387</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.42587</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36025</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36608</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41871</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.56568</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.5517799999999999</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.54889</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.5517799999999999</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.5177200000000001</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.63297</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.45113</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.51705</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.44887</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34368</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.5185599999999999</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.5751799999999999</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.63515</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.59824</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.67137</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.97414</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>1.31616</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.41491</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>1.21277</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>1.00066</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.98938</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.99095</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.56166</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.55189</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.94399</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>1.08376</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.7913</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.01077</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.77531</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.65586</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.64859</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.7159</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.79708</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.29481</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.7666900000000001</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.35468</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.49094</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.16205</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.9893500000000001</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.65516</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.6313</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.66493</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.6783</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.67336</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.65035</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.67484</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.20676</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.70778</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.78956</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1.70507</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.71284</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.721</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>1.63993</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.75529</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>1.01918</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>1.1286</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.6989</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.70734</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.70112</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.78074</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.7309</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.8200599999999999</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.6715099999999999</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.4649</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>1.175</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.55664</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.67155</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.54708</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.5804600000000001</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.34443</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.34481</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.5415</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.69171</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1.27699</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.56733</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.63175</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.34545</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.39235</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.35527</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.58116</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.3464100000000001</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.55386</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.65413</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.6323799999999999</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.62995</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.55869</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.34082</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.34324</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.53283</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.34089</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33582</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.35121</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.39814</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.40262</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.34491</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.42685</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.75338</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.4954</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.51346</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.5219400000000001</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34211</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.30127</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28471</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.34421</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.34153</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32794</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.34466</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.33613</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.4079</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.45337</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.92945</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.48266</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.18895</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.90034</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.7616900000000001</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.44965</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.39422</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.45713</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.5000899999999999</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.50002</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.45066</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.49158</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.3677</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36162</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36793</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39307</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.4029700000000001</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36956</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34929</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35551</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34181</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36932</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.34105</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.40584</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.3454700000000001</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.40586</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30053</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.34468</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.53074</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.3947</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.36928</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.33977</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.34219</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.45058</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.75297</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.42782</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.51791</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1.70084</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.49842</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.40681</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.42007</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.42841</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.35445</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.42283</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5660499999999999</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38967</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.42644</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.45516</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35241</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.40156</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.66916</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.45026</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.45178</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38358</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.43036</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40911</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38577</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38516</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65181</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83158</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47208</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40269</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45941</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34479</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.61334</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.57839</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.57347</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.97825</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.56177</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.50693</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.4801</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.44906</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.42733</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.37695</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.43885</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.51578</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.41833</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.54464</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.75991</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.34534</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.36049</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.76642</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.33166</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.27852</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.48279</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.39386</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.5442400000000001</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.50093</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.3605</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.72014</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.76064</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.55302</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.50105</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.45053</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>1.0181</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.4825</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1.44306</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.09144</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>1.12707</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.08023</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.36912</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1.11077</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>1.12741</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.01734</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.19308</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.14136</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.13031</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.1756</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.8418099999999999</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.19057</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.8480700000000001</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.34011</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.90146</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.70926</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.756</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.9470299999999999</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.49504</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.63251</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.62146</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.6641</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36016</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.75988</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.41057</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.55926</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.4277</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.60748</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.77907</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.77073</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.62027</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.60258</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.7215</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.73727</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.6169</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.7487699999999999</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.62329</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.72862</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.57638</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.51979</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.5255299999999999</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.5254800000000001</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.5763400000000001</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.45385</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.5385599999999999</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.46315</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.70074</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.5859500000000001</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.53874</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.77983</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.59785</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.10565</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.79739</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.35929</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.7604299999999999</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>1.29866</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>1.35919</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.74129</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.66338</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1.36756</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>1.00433</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.60983</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.50032</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.50063</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.54816</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.59966</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.7504299999999999</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>1.19967</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.70501</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.93714</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.67979</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.9589099999999999</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.90327</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.76283</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.73249</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>1.18499</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.18617</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.44877</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.26231</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.66198</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.24594</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.29296</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.11067</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.43378</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>1.04102</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.81971</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.7721399999999999</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.4394</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.25108</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.6690700000000001</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.48555</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.5427999999999999</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.46413</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42656</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44839</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41786</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45773</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40707</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38858</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37684</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39026</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36649</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.44961</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.48745</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.40527</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.53163</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39428</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.53463</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.79914</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.68323</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.66557</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.50405</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>1.08458</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.69015</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.66522</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.80206</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.07978</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.19276</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.50013</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.19827</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.5466799999999999</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.15876</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.5573899999999999</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.57085</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.42751</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.50169</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.34272</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.37361</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.42949</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.48223</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.46273</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.50657</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.5109900000000001</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.46036</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41266</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.43317</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.54292</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.52086</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.6063500000000001</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.3846</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4060299999999999</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40312</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36536</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39931</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38196</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39386</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36413</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.76083</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.13858</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.7821399999999999</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.65843</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.48569</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.42414</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.39837</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37699</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.41267</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.38425</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.39966</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.38106</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.34296</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.41991</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.34771</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.42059</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.34565</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.3429700000000001</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.33848</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.4361</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.38361</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.5004</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.32567</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04337</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.36746</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.34229</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.46251</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.33273</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.31026</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.32573</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.44996</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.29942</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.36073</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.37661</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.36132</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.41289</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.44636</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.48359</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.44973</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.40013</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.46377</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.45054</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.46485</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.34443</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.55357</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.39276</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.44985</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.42525</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39843</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.41259</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37713</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.46129</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.42024</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.46918</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.5946</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.56768</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.57239</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.59077</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.5520499999999999</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.45243</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.41806</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.38433</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.38451</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.9578099999999999</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.44765</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.58935</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.45157</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.46041</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.53363</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.5272899999999999</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.52222</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.5219</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.33366</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.33479</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.33406</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.33233</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.33315</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.33233</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.33265</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.33322</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.33627</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.37229</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.38329</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.23454</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.30755</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.27279</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.3885</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.38811</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.34525</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.30027</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.30609</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.34236</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.15195</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.73576</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.21325</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.38711</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.30105</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.27261</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.13884</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.40454</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.34235</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.37427</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.33388</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.35402</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.69914</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.5676599999999999</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.30601</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.30603</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.28943</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.30743</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.32193</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.49954</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.38731</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.37481</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.34539</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.39189</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.62891</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.3665</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.39269</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.35468</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.36734</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.38306</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.37211</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.40005</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.38294</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.41695</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.43195</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.42883</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.39785</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.39311</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.38305</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.39323</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.3826</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.42895</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.80843</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.3837</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.46802</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.39324</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.3893</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.38927</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.38601</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.40266</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.37096</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.49041</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.10284</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.38493</v>
+      </c>
+      <c r="E137" t="n">
+        <v>1.02266</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.94589</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.52589</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.7607</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.76039</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.51534</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.41781</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.42948</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.42717</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.40926</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.41636</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.39589</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.44524</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.55938</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.36034</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.42745</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.38896</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.44491</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.60249</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>1.01566</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.42594</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.6691900000000001</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.80402</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.45522</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.40356</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.7602100000000001</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.41242</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.52926</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.38533</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.38868</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.24286</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>1.0872</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.98536</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.31562</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.6353</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.5515099999999999</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.38888</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.49767</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.5834199999999999</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.7605599999999999</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.5507300000000001</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.5492</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.39681</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.23555</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.36209</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.76416</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.76149</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.58453</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.45264</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.49816</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>1.01228</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.77188</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.6279</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.76064</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>1.20335</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.6085499999999999</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.7500800000000001</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.6388400000000001</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>1.26674</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.90035</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.88473</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.90526</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.92384</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>1.17571</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.6505599999999999</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.9585</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.69402</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.98438</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.65758</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.67636</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.75902</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.65806</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.26362</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1.04452</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>1.02452</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.03385</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.54729</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.36398</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.05835</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.41064</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.38154</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.76003</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.38999</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.34552</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.55969</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.80745</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.5527300000000001</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.75682</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.75864</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.56229</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.4708</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.46031</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.40807</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.42947</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.42014</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35857</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.37098</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.35524</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.38677</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.38379</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.36869</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.36059</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.35223</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.36192</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.38354</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.42321</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.4058</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.42772</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.63807</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.59573</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.5637300000000001</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.5427999999999999</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.45252</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.48143</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.49998</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.56038</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.81364</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.17657</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.13287</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.04577</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>1.1356</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.74894</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.74369</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.05661</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>1.07497</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.68328</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.55463</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.5610700000000001</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.5606599999999999</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.47992</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.28819</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.48355</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.34867</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.54984</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.55059</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.5466799999999999</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.66195</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.55559</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>1.05205</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.66275</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.55003</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.49995</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.5002</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.48289</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.5000599999999999</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.48252</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.5003</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.5783400000000001</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.55801</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.56174</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.4983399999999999</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.51424</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.40349</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.40033</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.38453</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.42353</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.5007699999999999</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.5617300000000001</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.66174</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>1.17469</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>1.07814</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.6624</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.58373</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>1.16489</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.87109</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.6619299999999999</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>1.16265</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.83701</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.49702</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.51209</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.49948</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.43994</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.53543</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.39194</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.39947</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.3445299999999999</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.88354</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.67289</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.6805099999999999</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.95762</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.65691</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.47604</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.3989</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.42011</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.40781</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.39332</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.36487</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.36318</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.35315</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.35413</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.35049</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.36164</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.34346</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.36236</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.38747</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.62993</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.58969</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.42219</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.64202</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.03038</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.21466</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.9337300000000001</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.98573</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>1.03331</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.97641</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.94374</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.9742999999999999</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.9572200000000001</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.9418099999999999</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.94428</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.43972</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.76883</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>1.14167</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.72046</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>1.1377</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>1.22387</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>1.20572</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.72703</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.9473400000000001</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.86749</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.93444</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.54919</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.69002</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.71252</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.76088</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.21051</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1.09076</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>1.03044</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.41798</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.34216</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.0259</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.12484</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.92977</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.7638200000000001</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.763</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.82282</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.7060700000000001</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42434</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.6905</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.56694</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40168</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45852</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.69245</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.74037</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.69945</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36323</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.3687</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.76007</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40113</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40117</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.3757799999999999</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.36462</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.40361</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.38881</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.70963</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.46541</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.74902</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.52407</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.5105299999999999</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.4435</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>1.02323</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.92089</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>1.03351</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.9308200000000001</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>1.04133</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>1.02416</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>1.02435</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1.28222</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1.09426</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>1.20815</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.56377</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.37597</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.68033</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.62307</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.7361799999999999</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.72136</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>1.02318</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.72122</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.77424</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>1.14858</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1.33618</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.54951</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.73872</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.31673</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.48133</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>1.08811</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.51849</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.49773</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.77214</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.53962</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.54144</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39832</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.81271</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.7679400000000001</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.80811</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.6801699999999999</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37511</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27097</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.45936</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.38836</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.36764</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.75998</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34958</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.43974</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.41847</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.37281</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.37631</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.35886</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.35898</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.36061</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.36694</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.35884</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.35726</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.35961</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.37291</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.49992</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.35828</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.38195</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.80914</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>1.30998</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>1.00153</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.93164</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.95787</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>1.03604</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.1639</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.06983</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.86188</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.69228</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.23705</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.2135</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.21472</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.14795</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.86434</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.3287</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.70111</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1.09297</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>1.10445</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.10449</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.13297</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.10214</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.5194</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.19752</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.65644</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.58424</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>1.15265</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.7474299999999999</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.67849</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>1.1818</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.87261</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>1.07174</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>1.06243</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>1.09129</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>1.03841</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1.06673</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>1.12511</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>1.0482</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>1.05881</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.1827</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.16149</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.23654</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.2016</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.29616</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.16755</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>1.17719</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>1.11761</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.09824</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>1.12427</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>1.1739</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>1.19136</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.17197</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>1.10974</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.6888200000000001</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.6259600000000001</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.57474</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.55555</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.44858</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.37915</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37557</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.54469</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.31034</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1.3078</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1.06532</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.48116</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.51932</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.4925</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39872</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.46289</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.46127</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.47684</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.49142</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.47854</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.39321</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38503</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.48473</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.48002</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.47801</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.47396</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.47723</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.46978</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.45915</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.4572</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.44792</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.45582</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.37232</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.84803</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.46563</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.37411</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.5761499999999999</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.69937</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.71496</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.66632</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.95521</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.7668700000000001</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.96057</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.17246</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>1.32569</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1.46948</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>1.45664</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.45643</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.56794</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>1.2663</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.85048</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.69028</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.73627</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.70002</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>1.50157</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.84374</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.8814299999999999</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>1.24279</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.77527</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.57931</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.58478</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.6425599999999999</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.7251599999999999</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.60348</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.7504299999999999</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.62524</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>1.21445</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1.18901</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.41744</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>1.19095</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>1.18754</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>1.1945</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>1.12504</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>1.09933</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>1.20684</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>1.12636</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>1.21248</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>1.07317</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>1.10281</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>1.20584</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>1.10763</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>1.55183</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.8100599999999999</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.8037300000000001</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.56388</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.38087</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1.23009</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.84873</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.84922</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.55892</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.55441</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.5629299999999999</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.51536</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.55377</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41962</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.5210499999999999</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.50112</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.45964</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.45987</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.38097</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.43856</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.39903</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.41204</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.49494</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.49901</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.5474</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.5198400000000001</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.5201399999999999</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.55708</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1.17481</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.88242</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1.49277</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>1.19928</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.50823</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.5699</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.8445199999999999</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.79552</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.59715</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.85193</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.50429</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.52138</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.54544</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>1.17609</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.70047</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.55459</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.18123</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.54853</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.5492400000000001</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.58029</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.79903</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.55415</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.7972400000000001</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.84848</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>1.17331</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.79804</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.68311</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>1.0826</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>1.17475</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>1.1793</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>1.18295</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>1.18077</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.8222200000000001</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.7350399999999999</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.6535</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.6843400000000001</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.6928099999999999</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.7333099999999999</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.8332200000000001</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.81659</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.62118</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.8148</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.76389</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>1.14322</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.76518</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.60897</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.6494</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.64554</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.6201</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.61605</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.7184299999999999</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.67791</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.82682</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.7038300000000001</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.60799</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.5308999999999999</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.51239</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40856</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40972</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38405</v>
       </c>
     </row>
   </sheetData>
